--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t xml:space="preserve">Componente </t>
   </si>
@@ -79,6 +79,24 @@
   </si>
   <si>
     <t>Set cacciaviti 14 pz</t>
+  </si>
+  <si>
+    <t>Kaiweets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multimetro digitale professionale </t>
+  </si>
+  <si>
+    <t>YIHUA 926LED-IV</t>
+  </si>
+  <si>
+    <t>stazione di saldatura 60W 90-480 °C</t>
+  </si>
+  <si>
+    <t>Owootecc filo saldante</t>
+  </si>
+  <si>
+    <t>filo disaldatura senza piombo 0,6 mm</t>
   </si>
 </sst>
 </file>
@@ -120,7 +138,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -143,23 +161,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -172,7 +179,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -459,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D10"/>
+  <dimension ref="A2:D12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -469,16 +475,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -539,10 +545,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -553,35 +559,74 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>6.99</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>6.99</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7">
+        <v>49.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="7">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
